--- a/src/MxDBUnit/resources/mxdbunit/sample/sample3.xlsx
+++ b/src/MxDBUnit/resources/mxdbunit/sample/sample3.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\MxDBUnit\src\MxDBUnit\resources\mxdbunit\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A10211-BCDB-4C30-8373-F3A2CF1779C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABC7D01-D0C5-4216-B240-7E9341DE2E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51192" yWindow="-6492" windowWidth="25452" windowHeight="19584" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37920" yWindow="-6600" windowWidth="26736" windowHeight="18396" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MxDBUnit.CustomerNPE" sheetId="4" r:id="rId1"/>
-    <sheet name="=MxDBUnit.CustomerNPE" sheetId="5" r:id="rId2"/>
+    <sheet name="#ReadMe" sheetId="6" r:id="rId1"/>
+    <sheet name="MxDBUnit.CustomerNPE" sheetId="4" r:id="rId2"/>
+    <sheet name="=MxDBUnit.CustomerNPE" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1"/>
@@ -65,6 +66,10 @@
   </si>
   <si>
     <t>Customer_002_NPE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Please refer to the "#ReadMe" sheet in "sample1.xlsx".</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -389,6 +394,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B42173F-35B9-49C4-9C3F-28933F860FC9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AEE99C2-9E27-465E-B6CB-6A2D58F84035}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
@@ -447,7 +468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05855E9E-4A78-4337-A1E6-41A1A78B0F61}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>

--- a/src/MxDBUnit/resources/mxdbunit/sample/sample3.xlsx
+++ b/src/MxDBUnit/resources/mxdbunit/sample/sample3.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\MxDBUnit\src\MxDBUnit\resources\mxdbunit\sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABC7D01-D0C5-4216-B240-7E9341DE2E5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B183B19-A5C9-463B-B0D8-0E27F84F4381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37920" yWindow="-6600" windowWidth="26736" windowHeight="18396" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40284" yWindow="-4524" windowWidth="21744" windowHeight="10188" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="#ReadMe" sheetId="6" r:id="rId1"/>
-    <sheet name="MxDBUnit.CustomerNPE" sheetId="4" r:id="rId2"/>
-    <sheet name="=MxDBUnit.CustomerNPE" sheetId="5" r:id="rId3"/>
+    <sheet name="#Alias" sheetId="7" r:id="rId2"/>
+    <sheet name="MxDBUnit.CustomerNPE" sheetId="4" r:id="rId3"/>
+    <sheet name="=MxDBUnit.CustomerNPE" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,8 +27,35 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>suzuki yuta</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{57541FA4-CD2D-4764-A6FB-955D94D01EBB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>If an entity name or table name is too long to be used as a sheet name, you can specify a shortened name in the AliasName field and the actual name in the OriginalName field; the conversion will then be performed at runtime.
+For an external database, specify only the table name in the AliasName field.
+For an internal database, match the inclusion or exclusion of the module name to the sheet name.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1"/>
@@ -70,6 +98,14 @@
   </si>
   <si>
     <t>Please refer to the "#ReadMe" sheet in "sample1.xlsx".</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AliasName</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>OriginalName</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -77,7 +113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +127,14 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -396,9 +440,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B42173F-35B9-49C4-9C3F-28933F860FC9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -410,9 +454,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4365A85-19D1-4B36-9944-A6A20EADF439}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AEE99C2-9E27-465E-B6CB-6A2D58F84035}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="17.296875" customWidth="1"/>
     <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
@@ -420,7 +488,7 @@
     <col min="4" max="4" width="15.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,7 +502,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -448,7 +516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -468,10 +536,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05855E9E-4A78-4337-A1E6-41A1A78B0F61}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="18.09765625" customWidth="1"/>
     <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
@@ -479,7 +547,7 @@
     <col min="4" max="4" width="15.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -507,7 +575,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>9</v>
       </c>
